--- a/inst/resources/tool_household_iphra_v2.xlsx
+++ b/inst/resources/tool_household_iphra_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection lockStructure="1" workbookAlgorithmName="SHA-512" workbookHashValue="h2fYSiQvhiNGkrtUsLkSn45g315KWDSA25bD4j3ORM5bRlKWMnBDtzvS6AbBSYAj6ag3ODyY1mEUTQPcGFJ0Tg==" workbookSaltValue="IfpCe47h0g637JARLrp1Sg==" workbookSpinCount="100000"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read_Me" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Read_Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'survey'!$B$1:$R$337</definedName>
@@ -995,42 +995,42 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>label::French (fr)</t>
+          <t>label::French</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>hint::French (fr)</t>
+          <t>hint::French</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>label::Arabic (ar)</t>
+          <t>label::Arabic</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>hint::Arabic (ar)</t>
+          <t>hint::Arabic</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>label::Spanish (sp)</t>
+          <t>label::Spanish</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>hint::Spanish (sp)</t>
+          <t>hint::Spanish</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>label::English (en)</t>
+          <t>label::English</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>hint::English (en)</t>
+          <t>hint::English</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
@@ -15590,22 +15590,22 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>label::French (fr)</t>
+          <t>label::French</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>label::Arabic (ar)</t>
+          <t>label::Arabic</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>label::Spanish (sp)</t>
+          <t>label::Spanish</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>label::English (en)</t>
+          <t>label::English</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">

--- a/inst/resources/tool_household_iphra_v2.xlsx
+++ b/inst/resources/tool_household_iphra_v2.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3225ED6A-2B4C-4FF0-88A2-42B8DD174FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465C8FD2-24B9-4679-AC9A-E97D025C7A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="h2fYSiQvhiNGkrtUsLkSn45g315KWDSA25bD4j3ORM5bRlKWMnBDtzvS6AbBSYAj6ag3ODyY1mEUTQPcGFJ0Tg==" workbookSaltValue="IfpCe47h0g637JARLrp1Sg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -11276,7 +11276,7 @@
     </row>
     <row r="7" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
-        <v>10501</v>
+        <v>10500</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>1741</v>
@@ -11301,7 +11301,7 @@
     </row>
     <row r="8" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
-        <v>10501</v>
+        <v>10500</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>1747</v>
@@ -11332,7 +11332,7 @@
     </row>
     <row r="9" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
-        <v>10501</v>
+        <v>10500</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>1747</v>
@@ -11360,7 +11360,7 @@
     </row>
     <row r="10" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
-        <v>10501</v>
+        <v>10500</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>1747</v>
@@ -11388,7 +11388,7 @@
     </row>
     <row r="11" spans="1:22" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
-        <v>10501</v>
+        <v>10500</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>1741</v>
@@ -12441,7 +12441,7 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
-        <v>10000</v>
+        <v>10101</v>
       </c>
       <c r="B50" t="s">
         <v>1858</v>
@@ -12469,8 +12469,8 @@
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A51" s="4">
-        <v>10000</v>
+      <c r="A51" s="41">
+        <v>10105</v>
       </c>
       <c r="B51" t="s">
         <v>1847</v>
@@ -12542,8 +12542,8 @@
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
-        <v>10000</v>
+      <c r="A53" s="41">
+        <v>10105</v>
       </c>
       <c r="B53" t="s">
         <v>1834</v>
@@ -12571,8 +12571,8 @@
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A54" s="4">
-        <v>10000</v>
+      <c r="A54" s="41">
+        <v>10103</v>
       </c>
       <c r="B54" t="s">
         <v>1904</v>
@@ -12606,8 +12606,8 @@
       </c>
     </row>
     <row r="55" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="4">
-        <v>10000</v>
+      <c r="A55" s="41">
+        <v>10103</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>1904</v>
@@ -32104,9 +32104,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C26:N26"/>
-    <mergeCell ref="C4:N4"/>
-    <mergeCell ref="C20:N20"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="C6:N6"/>
@@ -32120,14 +32117,17 @@
     <mergeCell ref="C18:N18"/>
     <mergeCell ref="C9:N9"/>
     <mergeCell ref="C21:N21"/>
+    <mergeCell ref="C10:N10"/>
+    <mergeCell ref="C16:N16"/>
+    <mergeCell ref="C26:N26"/>
+    <mergeCell ref="C4:N4"/>
+    <mergeCell ref="C20:N20"/>
+    <mergeCell ref="C25:N25"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="C22:N22"/>
     <mergeCell ref="C12:N12"/>
     <mergeCell ref="C11:N11"/>
     <mergeCell ref="C23:N23"/>
-    <mergeCell ref="C10:N10"/>
-    <mergeCell ref="C16:N16"/>
-    <mergeCell ref="C25:N25"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="C22:N22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
